--- a/tests/fixtures/excel/bien-chuan-hoa.xlsx
+++ b/tests/fixtures/excel/bien-chuan-hoa.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Ngày vào Đảng chính thức</t>
+          <t>Ngày vào Đảng (dự bị)</t>
         </is>
       </c>
     </row>
